--- a/samples/03_ds_rui_ro.xlsx
+++ b/samples/03_ds_rui_ro.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Cơ quan điều tra - UPDATE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Công văn 4532" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="524 DN" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,72 +415,186 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>MST</t>
+          <t>STT</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Cột 2</t>
+          <t>MÃ SỐ THUẾ</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Cột 3</t>
+          <t>TÊN CÔNG TY</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Cột 4</t>
+          <t>MÃ SỐ THUẾ</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>ĐƠN VỊ QUẢN LÝ THUẾ</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Văn bản</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Cột 6</t>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Ngày</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Cơ quan ban hành</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Vụ án liên quan</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Mức rủi ro</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>0312345678</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>CV số 123/CT-TTKT ngày 01/03/2026</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-    </row>
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0312816241</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CÔNG TY RƯỢU XYZ</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1396/YC-ANĐT-P6</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0313025323</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CÔNG TY GOLF</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1396/YC-ANĐT-P6</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A3:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Tên người nộp thuế</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Mã số thuế</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Cơ quan thuế</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Mức rủi ro</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CÔNG TY VPP</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>9999999999</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>TB số 456/TCT ngày 15/04/2026</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>524 DN RỦI RO THEO Công văn số 1798/TCT-TTKT ngày 16/5/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Mã số thuế</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>0400111222</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/samples/03_ds_rui_ro.xlsx
+++ b/samples/03_ds_rui_ro.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cơ quan điều tra - UPDATE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Công văn 4532" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="524 DN" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cơ quan điều tra - UPDATE" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Công văn 4532" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="524 DN" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,12 +549,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CÔNG TY VPP</t>
+          <t>CÔNG TY QUÀ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>9999999999</t>
+          <t>0400111222</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -592,7 +592,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0400111222</t>
+          <t>0301224067</t>
         </is>
       </c>
     </row>
